--- a/TME 2-1/Attendance TME 2-1.xlsx
+++ b/TME 2-1/Attendance TME 2-1.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\TME\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B55401-5C3B-492D-BF99-61D8ACD03FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3A8550-D59C-4910-94CD-2E831F712837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1" sheetId="2" r:id="rId1"/>
+    <sheet name="Assignment" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1'!$A$3:$Y$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1'!$A$3:$X$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="45">
   <si>
     <t>SL</t>
   </si>
@@ -175,7 +155,25 @@
     <t>Attendance%</t>
   </si>
   <si>
-    <t>Marks</t>
+    <t>Assignment 1</t>
+  </si>
+  <si>
+    <t>Knitting Action</t>
+  </si>
+  <si>
+    <t>Assignmnet 2</t>
+  </si>
+  <si>
+    <t>Assignment 3</t>
+  </si>
+  <si>
+    <t>Assignmnet 4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -285,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -317,10 +315,19 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -328,7 +335,7 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -346,186 +353,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -805,31 +632,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1" style="2" customWidth="1"/>
-    <col min="6" max="6" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="25" width="25.77734375" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="24" width="25.77734375" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="12"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="E1" s="8"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
@@ -849,9 +676,8 @@
       <c r="V1" s="8"/>
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -863,84 +689,83 @@
         <v>36</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="E2" s="9">
+        <v>1</v>
+      </c>
       <c r="F2" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="9">
-        <v>5</v>
+        <f>I2+1</f>
+        <v>6</v>
       </c>
       <c r="K2" s="9">
-        <f>J2+1</f>
-        <v>6</v>
+        <f t="shared" ref="K2:X2" si="0">J2+1</f>
+        <v>7</v>
       </c>
       <c r="L2" s="9">
-        <f t="shared" ref="L2:Y2" si="0">K2+1</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="M2" s="9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" s="9">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" s="9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P2" s="9">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="9">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R2" s="9">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S2" s="9">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" s="9">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U2" s="9">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>T2+1</f>
+        <v>17</v>
       </c>
       <c r="V2" s="9">
-        <f>U2+1</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="W2" s="9">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X2" s="9">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y2" s="9">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -953,20 +778,20 @@
       <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
+      <c r="E3" s="4">
+        <v>46250</v>
       </c>
       <c r="F3" s="4">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="G3" s="4">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="H3" s="4">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="I3" s="4">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -983,9 +808,8 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -995,13 +819,12 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="12">
-        <f>COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.75</v>
-      </c>
-      <c r="E4" s="1" t="str" cm="1">
-        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,"7.5",D4&gt;=80%,"6.5",D4&gt;=70%,"5.5",D4&gt;=60%,"4.5",D4&lt;60%,"0")</f>
-        <v>5.5</v>
+      <c r="D4" s="11">
+        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>32</v>
@@ -1009,11 +832,11 @@
       <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1030,9 +853,8 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A31" si="1">A4+1</f>
         <v>2</v>
@@ -1043,13 +865,12 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="12">
-        <f t="shared" ref="D5:D31" si="2">COUNTIF(F5:Y5,"P")/(COUNTIF(F5:Y5,"P")+COUNTIF(F5:Y5,"A"))</f>
+      <c r="D5" s="11">
+        <f t="shared" ref="D5:D31" si="2">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="str" cm="1">
-        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,"7.5",D5&gt;=80%,"6.5",D5&gt;=70%,"5.5",D5&gt;=60%,"4.5",D5&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>32</v>
@@ -1078,9 +899,8 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1091,13 +911,12 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="str" cm="1">
-        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,"7.5",D6&gt;=80%,"6.5",D6&gt;=70%,"5.5",D6&gt;=60%,"4.5",D6&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>32</v>
@@ -1126,9 +945,8 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1139,13 +957,12 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="str" cm="1">
-        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,"7.5",D7&gt;=80%,"6.5",D7&gt;=70%,"5.5",D7&gt;=60%,"4.5",D7&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>32</v>
@@ -1174,9 +991,8 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1187,13 +1003,12 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="str" cm="1">
-        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,"7.5",D8&gt;=80%,"6.5",D8&gt;=70%,"5.5",D8&gt;=60%,"4.5",D8&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>32</v>
@@ -1222,9 +1037,8 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1235,25 +1049,24 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="1" t="str" cm="1">
-        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,"7.5",D9&gt;=80%,"6.5",D9&gt;=70%,"5.5",D9&gt;=60%,"4.5",D9&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="11">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="G9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1270,9 +1083,8 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1283,25 +1095,24 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="1" t="str" cm="1">
-        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,"7.5",D10&gt;=80%,"6.5",D10&gt;=70%,"5.5",D10&gt;=60%,"4.5",D10&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="D10" s="11">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1318,9 +1129,8 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1331,13 +1141,12 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="str" cm="1">
-        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,"7.5",D11&gt;=80%,"6.5",D11&gt;=70%,"5.5",D11&gt;=60%,"4.5",D11&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="D11" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>32</v>
@@ -1348,8 +1157,8 @@
       <c r="H11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>32</v>
+      <c r="I11" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1366,9 +1175,8 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1379,13 +1187,12 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="str" cm="1">
-        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,"7.5",D12&gt;=80%,"6.5",D12&gt;=70%,"5.5",D12&gt;=60%,"4.5",D12&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E12" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>32</v>
@@ -1414,9 +1221,8 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1427,13 +1233,12 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="str" cm="1">
-        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,"7.5",D13&gt;=80%,"6.5",D13&gt;=70%,"5.5",D13&gt;=60%,"4.5",D13&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -1462,9 +1267,8 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1475,13 +1279,12 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="str" cm="1">
-        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,"7.5",D14&gt;=80%,"6.5",D14&gt;=70%,"5.5",D14&gt;=60%,"4.5",D14&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="D14" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>32</v>
@@ -1492,8 +1295,8 @@
       <c r="H14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>32</v>
+      <c r="I14" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1510,9 +1313,8 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1523,22 +1325,21 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="1" t="str" cm="1">
-        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,"7.5",D15&gt;=80%,"6.5",D15&gt;=70%,"5.5",D15&gt;=60%,"4.5",D15&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="D15" s="11">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="F15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>32</v>
@@ -1558,9 +1359,8 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1571,13 +1371,12 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="str" cm="1">
-        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,"7.5",D16&gt;=80%,"6.5",D16&gt;=70%,"5.5",D16&gt;=60%,"4.5",D16&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>32</v>
@@ -1606,9 +1405,8 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1619,22 +1417,21 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="12">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="E17" s="1" t="str" cm="1">
-        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,"7.5",D17&gt;=80%,"6.5",D17&gt;=70%,"5.5",D17&gt;=60%,"4.5",D17&lt;60%,"0")</f>
-        <v>5.5</v>
+      <c r="D17" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>32</v>
@@ -1654,9 +1451,8 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1667,16 +1463,15 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="12">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="E18" s="1" t="str" cm="1">
-        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,"7.5",D18&gt;=80%,"6.5",D18&gt;=70%,"5.5",D18&gt;=60%,"4.5",D18&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>32</v>
+      <c r="D18" s="11">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>31</v>
@@ -1684,8 +1479,8 @@
       <c r="H18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>31</v>
+      <c r="I18" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1702,9 +1497,8 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1715,19 +1509,18 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="1" t="str" cm="1">
-        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,"7.5",D19&gt;=80%,"6.5",D19&gt;=70%,"5.5",D19&gt;=60%,"4.5",D19&lt;60%,"0")</f>
-        <v>0</v>
+      <c r="D19" s="11">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>31</v>
+      <c r="G19" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -1750,9 +1543,8 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1763,13 +1555,12 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="str" cm="1">
-        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,"7.5",D20&gt;=80%,"6.5",D20&gt;=70%,"5.5",D20&gt;=60%,"4.5",D20&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E20" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>32</v>
@@ -1798,9 +1589,8 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1811,13 +1601,12 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="str" cm="1">
-        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,"7.5",D21&gt;=80%,"6.5",D21&gt;=70%,"5.5",D21&gt;=60%,"4.5",D21&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E21" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>32</v>
@@ -1846,9 +1635,8 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1859,13 +1647,12 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="str" cm="1">
-        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,"7.5",D22&gt;=80%,"6.5",D22&gt;=70%,"5.5",D22&gt;=60%,"4.5",D22&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E22" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1894,9 +1681,8 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1907,13 +1693,12 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E23" s="1" t="str" cm="1">
-        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,"7.5",D23&gt;=80%,"6.5",D23&gt;=70%,"5.5",D23&gt;=60%,"4.5",D23&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E23" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>32</v>
@@ -1942,9 +1727,8 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1955,13 +1739,12 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="str" cm="1">
-        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,"7.5",D24&gt;=80%,"6.5",D24&gt;=70%,"5.5",D24&gt;=60%,"4.5",D24&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="D24" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>32</v>
@@ -1972,8 +1755,8 @@
       <c r="H24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>32</v>
+      <c r="I24" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1990,9 +1773,8 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -2003,13 +1785,12 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E25" s="1" t="str" cm="1">
-        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,"7.5",D25&gt;=80%,"6.5",D25&gt;=70%,"5.5",D25&gt;=60%,"4.5",D25&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E25" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>32</v>
@@ -2038,9 +1819,8 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -2051,22 +1831,21 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E26" s="1" t="str" cm="1">
-        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,"7.5",D26&gt;=80%,"6.5",D26&gt;=70%,"5.5",D26&gt;=60%,"4.5",D26&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="D26" s="11">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="F26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>32</v>
+      <c r="H26" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>31</v>
@@ -2086,9 +1865,8 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -2099,19 +1877,18 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="12">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="E27" s="1" t="str" cm="1">
-        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,"7.5",D27&gt;=80%,"6.5",D27&gt;=70%,"5.5",D27&gt;=60%,"4.5",D27&lt;60%,"0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>32</v>
@@ -2134,9 +1911,8 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -2147,16 +1923,15 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="12">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="1" t="str" cm="1">
-        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,"7.5",D28&gt;=80%,"6.5",D28&gt;=70%,"5.5",D28&gt;=60%,"4.5",D28&lt;60%,"0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="F28" s="5" t="s">
+      <c r="D28" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
@@ -2182,9 +1957,8 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -2195,16 +1969,15 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="12">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="E29" s="1" t="str" cm="1">
-        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,"7.5",D29&gt;=80%,"6.5",D29&gt;=70%,"5.5",D29&gt;=60%,"4.5",D29&lt;60%,"0")</f>
-        <v>5.5</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="D29" s="11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
@@ -2230,9 +2003,8 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -2243,13 +2015,12 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E30" s="1" t="str" cm="1">
-        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,"7.5",D30&gt;=80%,"6.5",D30&gt;=70%,"5.5",D30&gt;=60%,"4.5",D30&lt;60%,"0")</f>
-        <v>7.5</v>
+      <c r="E30" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>32</v>
@@ -2278,9 +2049,8 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -2291,25 +2061,24 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="12">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="E31" s="1" t="str" cm="1">
-        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,"7.5",D31&gt;=80%,"6.5",D31&gt;=70%,"5.5",D31&gt;=60%,"4.5",D31&lt;60%,"0")</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="D31" s="11">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2326,24 +2095,792 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:X31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
       <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
-      <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A66B3EF-818E-4A70-9374-2DAEC6B795EE}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="25.77734375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7">
+        <f>COUNT(A4:A31)</f>
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="15">
+        <v>20</v>
+      </c>
+      <c r="I3" s="15">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25011101001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <f>SUM(D4:G4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <f>(H4/20)*7.5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <f t="shared" ref="A5:A31" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25011101002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H31" si="1">SUM(D5:G5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" ref="I5:I31" si="2">(H5/20)*7.5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25011101003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25011101004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25011101005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25011101008</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25011101009</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25011101010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25011101011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25011101012</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25011101013</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25011101014</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25011101015</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25011101016</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25011101017</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25011101018</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25011101019</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25011101020</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25011101021</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25011101022</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25011101023</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25011101024</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25011101025</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25011101026</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25011101027</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25011101028</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25011101029</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25011101030</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="H1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D3:G3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>